--- a/TestReport.xlsx
+++ b/TestReport.xlsx
@@ -19,10 +19,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Age</t>
   </si>
   <si>
-    <t>Date</t>
+    <t>City</t>
   </si>
 </sst>
 </file>
